--- a/data/00 readme.xlsx
+++ b/data/00 readme.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanya\Desktop\MECH70038 - Research Project\Project Phase\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanya\Desktop\MECH70038 - Research Project\git\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960B117D-740A-4E28-8D3A-9FF2363ABDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E059F067-14FA-4CBE-97E4-4BD147F43FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Directory" sheetId="1" r:id="rId1"/>
@@ -21,193 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="281">
-  <si>
-    <t>DEMAND</t>
-  </si>
-  <si>
-    <t>- Floor area per activity: BEES median premises floor area (Figure 1.4, England and Wales) — see demand_profile_model.load_bees_floor_areas() for the source workbook/sheet.</t>
-  </si>
-  <si>
-    <t>- Electricity demand: lighting + small power + HVAC + EV + heat-pump electricity (if HP scenario)</t>
-  </si>
-  <si>
-    <t>- Demand grows across the 15-year horizon: non-heat electricity per the DESNZ Reference projection; heat demand falls and heat-pump COP improves as the climate warms, per the UKCP18 projection — see growth.py and datasets.get_electricity_projection() / get_climate_projection() (year-0 = EMISSIONS_BASE_YEAR in model_params.py).</t>
-  </si>
-  <si>
-    <t>- 24 representative days per year: 12 months × {WD, WE}. The WD/WE split applies wd_fac = 7/(5+2f) and we_fac = wd_fac × f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  where f = WE_LOAD_FACTOR[activity] from TM46 operational schedules — see model_params.py.</t>
-  </si>
-  <si>
-    <t>- WD/WE day counts per month are derived from a fixed representative calendar year — see optimisation_config.wd_we_counts_2025().</t>
-  </si>
-  <si>
-    <t>PV</t>
-  </si>
-  <si>
-    <t>- Cell temperature: T_cell = T_amb + cell_temp_coeff × I (I = irradiance, W/m²) — see PV sheet, cell_temp_coeff.</t>
-  </si>
-  <si>
-    <t>- PV capex = construction cost + infrastructure cost per kWp, each carrying its own DESNZ Low/Central/High scenario (one shared switch for both, Central active by default) — see PV sheet, const_per_kwp / infra_per_kwp, and PV_CAPEX_ACTIVE in model_params.py.</t>
-  </si>
-  <si>
-    <t>- PV and inverter degradation, and inverter replacement year + cost share — see PV sheet, soh_decay_per_yr / soh_inv_decay_per_yr / inv_replace_year / inv_cost_share.</t>
-  </si>
-  <si>
-    <t>- Maintenance and insurance are PV-specific £/MW/yr rates, each with its own Low/Central/High scenario — see PV sheet, maint_per_mw_per_yr / insurance_per_mw_per_yr. PV is the only technology with a separate insurance line (see ECONOMICS).</t>
-  </si>
-  <si>
-    <t>BATTERY (Li-ion)</t>
-  </si>
-  <si>
-    <t>- No separate commissioning cost: balance-of-system and commissioning are already embedded in the energy/power capex rates.</t>
-  </si>
-  <si>
-    <t>HEAT: Scenario parameter</t>
-  </si>
-  <si>
-    <t>- Useful thermal demand is tech-independent; same WD/WE scaling as electricity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  COP is computed in demand_profile_model.py — ASHP follows the outdoor-temperature curve hourly; GSHP follows a flat curve for vertical loops and a temperature-varying curve for horizontal loops.</t>
-  </si>
-  <si>
-    <t>- Heat-pump replacement year, and the GSHP HP-unit-vs-ground-loop capex split used at replacement (the loop outlasts the horizon) — see Heating sheet, replace_year / replace_cost_share.</t>
-  </si>
-  <si>
-    <t>- New-build vs retrofit (NEW_BUILD flag, optimisation_config.py): new-build installs a fresh boiler on the BAU and every scenario alike (gas capex cancels for a gas-vs-gas comparison; a heat-pump scenario gets an avoided-boiler credit). Retrofit treats the existing gas boiler as a sunk asset for a gas-boiler scenario (no capex, no replacement) and instead charges a heat-pump scenario a one-off fixed gas-service decommissioning cost with no avoided-boiler credit — see Heating sheet, decommission_fixed.</t>
-  </si>
-  <si>
-    <t>- GSHP horizontal-vs-vertical land-area constraint not yet applied — both loop types are selectable on cost/COP alone.</t>
-  </si>
-  <si>
-    <t>FUEL &amp; ELECTRICITY IMPORT PRICING</t>
-  </si>
-  <si>
-    <t>- Electricity import price: a wholesale + regional DUoS build-up (wholesale × half-hourly shape + per-DNO DUoS Red/Amber/Green + CCL + band-specific residual), giving an intra-day, seasonal, regional price rather than one flat rate — see pricing.py and Energy Prices sheet (DUoS Time Band / DUoS Unit Charge / Retail Non-Commodity groups); wholesale level from api_wholesale_prices.py.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Can be switched off in favour of the flat DESNZ band price — see optimisation_config.USE_WHOLESALE_DUOS_BUILDUP.</t>
-  </si>
-  <si>
-    <t>- Export price: SEG Low/Central/High sensitivities; real escalation from the electricity price-growth scenario — see Energy Prices sheet (Electricity Export group).</t>
-  </si>
-  <si>
-    <t>ROOF (per activity class — see ROOF_PROPERTIES)</t>
-  </si>
-  <si>
-    <t>- Roof footprint = BEES floor area / median storeys. Median storeys per activity read from the OpenStreetMap building:levels survey — see api_osm_storeys.py / data/api_osm_storeys.xlsx.</t>
-  </si>
-  <si>
-    <t>- Usable PV area = footprint × [ flat_share × pv_usable_frac × pv_inter_row_frac + (1-flat_share) × (1/cos(pitch)) × pitched_usable_slope_frac ],</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  i.e. flat roofs use the literature usable fractions below, further de-rated by inter-row self-shading (flat-roof PV is tilted/rack-mounted); pitched roofs have a larger sloped surface but a smaller usable share after orientation, shading and obstructions, and are mounted flush to the slope so no inter-row spacing applies.</t>
-  </si>
-  <si>
-    <t>PV irradiance</t>
-  </si>
-  <si>
-    <t>- Hourly shape from dm.solar_elevation_profile at the parent-season DOY (mid-season solar geometry)</t>
-  </si>
-  <si>
-    <t>- Ambient temperature per month uses monthly HDD via T_amb = T_base − HDD; hourly amplitude from dm.DIURNAL_AMPLITUDE at the parent-season level — see model_params.py, HDD_BASE / DIURNAL_AMPLITUDE.</t>
-  </si>
-  <si>
-    <t>- Horizon — see optimisation_config.HORIZON_YEARS.</t>
-  </si>
-  <si>
-    <t>- Maintenance and insurance are technology-specific, not one flat percentage: PV maintenance + insurance are £/MW/yr rates (PV sheet); battery and thermal-store maintenance are a % of their own capex/yr (Battery / Thermal Store sheets, maint_pct_capex); heating maintenance is £/kW_th/yr (Heating sheet, maint_per_kwth_per_yr). Only PV carries a separate insurance line.</t>
-  </si>
-  <si>
-    <t>- Real O&amp;M escalation — see Scalars sheet, general_inflation (the model runs in real prices, so this is 0 by construction unless overridden).</t>
-  </si>
-  <si>
-    <t>- All cost vintages are rebased to a common real price-basis year via the UK GDP deflator before use, so PV/battery/heating/carbon figures sourced in different base years are comparable — see Scalars sheet, GDP_DEFLATOR [year] rows, and model_params.py (TARGET_PRICE_YEAR) / each sheet's 'Price Base Year' column.</t>
-  </si>
-  <si>
-    <t>- No separate PV or thermal-store commissioning cost; battery and heat-pump commissioning are folded into their unit capex rates (see BATTERY / HEAT above).</t>
-  </si>
-  <si>
-    <t>- BAU baseline (common to all scenarios) = conventional gas boiler (sized to peak) + grid electricity + gas, no PV/battery/thermal store, with the same new-build/retrofit treatment as the scenario. NPV savings = BAU NPV − scenario NPV; both include heating-plant capex, so heating systems compare fairly.</t>
-  </si>
-  <si>
-    <t>GRID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    * Import ceiling = max(district import limit, building non-flexible baseline peak) — the DNO headroom is the binding cap, floored at the site's own baseline so it can always serve its load.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    * Export ceiling = district export limit (PV export is entirely new generation).</t>
-  </si>
-  <si>
-    <t>UNCERTAINTY — TWO-STAGE STOCHASTIC PROGRAM (TSSP)</t>
-  </si>
-  <si>
-    <t>- Uncertain input (this iteration): ELECTRICITY IMPORT price only. Two facets, both sampled:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    * annual escalation — triangular over the Energy Price Growth electricity band (Low/Central/High) — see Energy Prices sheet, Energy Price Growth group (elec_price_growth).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Level and escalation are sampled independently; each draw -&gt; a 15-yr price path level*(1+growth)^y.</t>
-  </si>
-  <si>
-    <t>CARBON (OF2) — lifetime operational emissions, kgCO2e</t>
-  </si>
-  <si>
-    <t>- Exported PV is CREDITED at the same long-run-marginal factor (avoided grid generation).</t>
-  </si>
-  <si>
-    <t>- Gas combustion: constant all-GHG factor (gross CV) — see Emissions sheet, Gas Emission Factor group.</t>
-  </si>
-  <si>
-    <t>OUT OF SCOPE</t>
-  </si>
-  <si>
-    <t>- Seasonal (inter-day) thermal storage; the buffer store is daily-cycling only</t>
-  </si>
-  <si>
-    <t>- Demand response / load shifting</t>
-  </si>
-  <si>
-    <t>- Embodied / lifecycle carbon of PV, battery, heat-pump plant (no UK-gov source; operational only)</t>
-  </si>
-  <si>
-    <t>- Uncertainty in demand, PV generation, gas and carbon prices (only electricity import price is built in)</t>
-  </si>
-  <si>
-    <t>- Frequency response revenue</t>
-  </si>
-  <si>
-    <t>- Type taxonomy (the Type column; live conditional formatting colours the row — edit via the dropdown):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    * Verifiable assumption — a specific source exists but the value is not yet confirmed against it; Source lists the citation to check.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    * Placeholder — interim value, not yet sourced; Source flags where to look ('TO BE SOURCED — …').</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    * Standing assumption — deliberate modelling / design choice or simplification with no single external citation (Source = '-').</t>
-  </si>
-  <si>
-    <t>- Demand-model coverage &amp; deferrals:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    * Included from demand_profile_model.py: heat-pump COP fits + envelopes, boiler efficiency, ground-loop thermal model, EV inputs, and climate/geometry/weekend-scaling constants.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    * Deferred to inputs.xlsx (data loaded from that workbook, or mappings tightly coupled to it): CIBSE Dashboard, NCM occupancy/setpoints, TM46 adjustment, BEES floor areas + base-load fractions, UKPN EV shape; plus the ACTIVITY_LOOKUP mappings, BASE_LOAD_CFG and area_weights vectors. Handle these when deciding what to do with inputs.xlsx.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    * Derived values: battery chg_eff/disc_eff = sqrt(round_trip_eff); BATT_MAX_KW = c_rate_chg × BATT_MAX_KWH; DAMPING_DEPTH_M = sqrt(2·alpha/omega) and _OMEGA_YR (demand model).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    * Solver / structural / calendar constants: timestep (T_RES_H, HH_PER_DAY), HORIZON_YEARS, BATT_MAX_KWH, MIP_GAP_REL, solver settings; MONTH_DAYS / MONTH_SEASON / MONTHS_ORDER. Model architecture, not empirical inputs.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="299">
   <si>
     <t>Data Layer</t>
   </si>
@@ -274,7 +88,8 @@
   <si>
     <t>1) Download and install iSBEM
 2) Extract ncmsbem.mdb
-3) Convert to .csv format</t>
+3) Convert to .csv format
+4) Operational profiles are in activity_sbem_L.csv</t>
   </si>
   <si>
     <t>https://www.uk-ncm.org.uk/download.jsp</t>
@@ -365,9 +180,6 @@
     <t>Tracked per parameter within sheet</t>
   </si>
   <si>
-    <t>https://assets.publishing.service.gov.uk/media/6218c5d38fa8f54911e22263/AD_S.pdf</t>
-  </si>
-  <si>
     <t>Demand: Climate &amp; demand-shape assumptions</t>
   </si>
   <si>
@@ -380,7 +192,7 @@
     <t>Per-activity weekday/weekend load factor, diurnal amplitude, solar-geometry reference dates, HDD base temperature</t>
   </si>
   <si>
-    <t>Feeds the intra-day demand shape and the sinusoid-temperature fallback. NOTE: no Source URL populated for this sheet yet</t>
+    <t>Feeds the intra-day demand shape and the sinusoid-temperature fallback. Source URLs are populated for the CIBSE Guide A diurnal-amplitude, TM46 weekend-load-factor and degreedays.net HDD-base rows; the solar-geometry reference DOYs and the numeric-tolerance/geometry constants carry a written source only</t>
   </si>
   <si>
     <t>Demand: Solar irradiance (GHI)</t>
@@ -396,9 +208,6 @@
   </si>
   <si>
     <t>Feeds the PV generation profile (daily_ghi_kwh_per_m2)</t>
-  </si>
-  <si>
-    <t>https://re.jrc.ec.europa.eu/pvg_tools/en/</t>
   </si>
   <si>
     <t>Demand: Location (Degree Days)</t>
@@ -472,7 +281,7 @@
     <t>climate_projection_output.csv</t>
   </si>
   <si>
-    <t>Derived - see /hdd (BizEE) and /climateprojections (UKCP18) rows above</t>
+    <t>Derived (projections.py) - see /hdd (BizEE) and /climateprojections (UKCP18) rows above</t>
   </si>
   <si>
     <t>Fitted monthly temperature distributions shifted by the UKCP18 ensemble-mean anomaly; projects future HDDs 2026-2080</t>
@@ -481,7 +290,7 @@
     <t>Auto-generated pipeline artifact, not manually downloaded</t>
   </si>
   <si>
-    <t>Auto-run: demand_profile_model.py invokes climate_projection.py as a subprocess on every run</t>
+    <t>Auto-run: demand_profile_model.py invokes projections.py as a subprocess on every run (run_sigma_fit -&gt; run_hdd_projection). Can also be regenerated on its own: python projections.py</t>
   </si>
   <si>
     <t>Demand: Electricity growth (derived output)</t>
@@ -490,13 +299,13 @@
     <t>electricity_projection_output.csv</t>
   </si>
   <si>
-    <t>DESNZ Annex F (already transcribed into Scalars sheet ELEC_DEMAND_TWH rows)</t>
+    <t>DESNZ Annex F (already transcribed into Scalars sheet ELEC_DEMAND_TWH rows); derived by projections.py</t>
   </si>
   <si>
     <t>Non-heating electricity demand growth factor per year (2026-2050), DESNZ Reference scenario</t>
   </si>
   <si>
-    <t>Auto-run: demand_profile_model.py invokes electricity_projection.py as a subprocess on every run</t>
+    <t>Auto-run: demand_profile_model.py invokes projections.py as a subprocess on every run (run_electricity_projection). Can also be regenerated on its own: python projections.py</t>
   </si>
   <si>
     <t>Demand: Roof storey survey</t>
@@ -547,22 +356,37 @@
     <t>https://archive-api.open-meteo.com/v1/archive</t>
   </si>
   <si>
+    <t>Demand: DEC metered validation</t>
+  </si>
+  <si>
+    <t>/.admin/display-csv/certificates-&lt;year&gt;.csv</t>
+  </si>
+  <si>
+    <t>Energy Performance of Buildings Register (MHCLG), England &amp; Wales</t>
+  </si>
+  <si>
+    <t>Display Energy Certificates (DEC) bulk data extract; DECs are operational ratings scored against the CIBSE TM46 benchmarks</t>
+  </si>
+  <si>
+    <t>Metered annual electricity and delivered-fuel intensities (kWh/m2/yr) for real buildings. Used to validate the modelled year-0 intensities from OUTSIDE the CIBSE/TM46 benchmark chain the profiles are built from, which is what the benchmark-vs-benchmark comparison could not do. Three-way per activity class: model / TM46 'typical_*' fields / DEC 'annual_*' metered actuals. Caveats restated in the output: DECs are issued to public-authority buildings only, and DEC applies at or above 250 m2, so smaller and private-sector premises are absent by design</t>
+  </si>
+  <si>
+    <t>https://epc.opendatacommunities.org/downloads/dec</t>
+  </si>
+  <si>
     <t>Optimisation: General scalars</t>
   </si>
   <si>
     <t>Scalars</t>
   </si>
   <si>
-    <t>HM Treasury Green Book; DESNZ Annex F; DNO headroom portals (see /headroom row above)</t>
-  </si>
-  <si>
-    <t>Discount rate, general inflation, FX planning rates, GDP deflator (real-terms rebasing), DESNZ Reference electricity-demand growth, grid import/export headroom per district</t>
-  </si>
-  <si>
-    <t>Mixed-scope sheet; each row individually cited via the sheet's own Source / Source URL columns</t>
-  </si>
-  <si>
-    <t>https://www.gov.uk/government/publications/the-green-book-appraisal-and-evaluation-in-central-government</t>
+    <t>HM Treasury Green Book; DESNZ Annex F; DNO headroom portals (see /headroom row above); NCM Modelling Guide 2021 Edition England</t>
+  </si>
+  <si>
+    <t>Discount rate, general inflation, FX planning rates, GDP deflator (real-terms rebasing), DESNZ Reference electricity-demand growth, grid import/export headroom per district, primary energy factors for electricity and gas</t>
+  </si>
+  <si>
+    <t>Mixed-scope sheet; each row individually cited via the sheet's own Source / Source URL columns. The PRIMARY_ENERGY_FACTOR rows are reporting-only (the primary-energy column on the MAC grid) and feed neither the cost nor the carbon objective</t>
   </si>
   <si>
     <t>Optimisation: Energy prices (wholesale/DUoS/CCL/SEG)</t>
@@ -580,9 +404,6 @@
     <t>Feeds pricing.py's shaped intra-day import price and the model's flat elec_export_price</t>
   </si>
   <si>
-    <t>https://www.gov.uk/government/statistical-data-sets/gas-and-electricity-prices-in-the-non-domestic-sector</t>
-  </si>
-  <si>
     <t>Optimisation: Emissions &amp; carbon values</t>
   </si>
   <si>
@@ -598,22 +419,19 @@
     <t>Feeds the carbon/emissions objective (OF2) and the MAC columns</t>
   </si>
   <si>
-    <t>https://www.gov.uk/government/publications/valuation-of-energy-use-and-greenhouse-gas-emissions-for-appraisal</t>
-  </si>
-  <si>
     <t>Optimisation: PV technology costs</t>
   </si>
   <si>
+    <t>PV</t>
+  </si>
+  <si>
     <t>CEP Technology Library v1.02; DESNZ (2024) Onshore Wind &amp; Solar cost assumptions; NREL cost benchmarks; Cayuela et al. (2024); Mondol, Yohanis &amp; Norton (2005)</t>
   </si>
   <si>
     <t>Module/inverter capex, cell efficiency, degradation rate, temperature coefficient, replacement year</t>
   </si>
   <si>
-    <t>Feeds PV sizing capex &amp; performance terms in build_milp</t>
-  </si>
-  <si>
-    <t>https://www.gov.uk/government/publications/onshore-wind-and-solar-cost-and-technical-assumptions</t>
+    <t>Feeds PV sizing capex &amp; performance terms in build_lp</t>
   </si>
   <si>
     <t>Optimisation: Battery technology costs</t>
@@ -631,9 +449,6 @@
     <t>Feeds battery sizing capex &amp; the SOC dynamics constraints</t>
   </si>
   <si>
-    <t>https://www.osti.gov/biblio/2583471</t>
-  </si>
-  <si>
     <t>Optimisation: Heating technology costs</t>
   </si>
   <si>
@@ -646,10 +461,7 @@
     <t>ASHP/GSHP/gas-boiler capex, decommissioning, gas-connection charges</t>
   </si>
   <si>
-    <t>Feeds heating-plant capex. NOTE: 3 rows still marked 'TO BE SOURCED' (trenching/borehole cost split, boiler strip-out placeholder) - flagged for follow-up</t>
-  </si>
-  <si>
-    <t>https://www.gov.uk/government/publications/evidence-update-of-low-carbon-heating-and-cooling-in-non-domestic-buildings</t>
+    <t>Feeds heating-plant capex, decommissioning and the replacement-year cost split. All rows are now sourced - no 'TO BE SOURCED' placeholders remain on this sheet</t>
   </si>
   <si>
     <t>Optimisation: Thermal store costs</t>
@@ -664,10 +476,7 @@
     <t>Hot-water buffer-tank capex, charge/discharge efficiency, standing loss</t>
   </si>
   <si>
-    <t>Feeds thermal-store sizing in the heat-side MILP</t>
-  </si>
-  <si>
-    <t>https://ens.dk/en/analyses-and-statistics/technology-data-energy-storage</t>
+    <t>Feeds thermal-store sizing in the heat-side LP</t>
   </si>
   <si>
     <t>Optimisation: Roof constraints</t>
@@ -685,9 +494,6 @@
     <t>Feeds n_pv_max (roof-area PV cap) per activity</t>
   </si>
   <si>
-    <t>https://iea-pvps.org/wp-content/uploads/2020/01/rep7_04.pdf</t>
-  </si>
-  <si>
     <t>Optimisation: Heat-pump COP curves</t>
   </si>
   <si>
@@ -712,16 +518,13 @@
     <t>Ground Loop (DM)</t>
   </si>
   <si>
-    <t>Banks (2008), Introduction to Thermogeology; Met Office UK climate extremes</t>
-  </si>
-  <si>
-    <t>Ground temperature, burial depth, carrier-fluid flow, brine offset for GSHP COP</t>
-  </si>
-  <si>
-    <t>Feeds the vertical/horizontal GSHP entering-fluid-temperature model</t>
-  </si>
-  <si>
-    <t>https://www.geokniga.org/bookfiles/geokniga-banksintroductiontothermogeology2008.pdf</t>
+    <t>Banks (2008), Introduction to Thermogeology; Met Office UK climate extremes; Zeh et al. (2022), Mapping Specific Heat Extraction for Very Shallow Geothermal Systems (Sustainability 14:4199); GLA London Employment Sites Database 2024</t>
+  </si>
+  <si>
+    <t>Ground temperature, burial depth, soil thermal diffusivity, brine offset for GSHP COP; plus the horizontal-loop land-availability parameters (collector area per kW_th, site plot ratio, gross land per parking space)</t>
+  </si>
+  <si>
+    <t>Feeds the vertical/horizontal GSHP entering-fluid-temperature model, and the land-area ceiling on GSHP (horizontal) heating capacity (optimisation_engine.land_limit_kwth: soft ground = site area - roof footprint - parking, divided by collector m2/kW_th). Vertical boreholes are unconstrained</t>
   </si>
   <si>
     <t>Optimisation: Grid connection limits</t>
@@ -796,9 +599,295 @@
     <t>https://data.elexon.co.uk/bmrs/api/v1/datasets/MID</t>
   </si>
   <si>
+    <t>Optimisation: ASHP sensitivity (alternative product)</t>
+  </si>
+  <si>
+    <t>ashp_grant_aerona3_sensitivity.py (module constants)</t>
+  </si>
+  <si>
+    <t>Grant UK - Aerona3 R32 air source heat pump, declared product performance data</t>
+  </si>
+  <si>
+    <t>Manufacturer declared COP at the A7/W55 rating point (EN 14511)</t>
+  </si>
+  <si>
+    <t>Benchmarks the model's CEP-library ASHP against a real UK product: COP @ A7/W55 = 2.66 vs the model's 2.7283 (-2.50%), paired with a 2.6% cut to HEAT_COSTS['ASHP']['capex_per_kwth']. The COP/temperature slope is held at the model's value (cold-weather sensitivity assumed identical). Stage-1 sizing is fixed at the saved deterministic design; only stage-2 dispatch is re-solved</t>
+  </si>
+  <si>
+    <t>1) Read the declared A7/W55 COP from the manufacturer's product data
+2) Set GRANT_COP_AT_7C / CAPEX_REDUCTION_FRAC in ashp_grant_aerona3_sensitivity.py
+3) Runs automatically at the end of optimisation_model.main(), or standalone: python ashp_grant_aerona3_sensitivity.py</t>
+  </si>
+  <si>
+    <t>https://www.grantuk.com/products/renewables/aerona3-air-source-heat-pumps/</t>
+  </si>
+  <si>
+    <t>Optimisation: PV sensitivity (alternative panel)</t>
+  </si>
+  <si>
+    <t>pv_panel1_sensitivity.py (module constants)</t>
+  </si>
+  <si>
+    <t>CEP Technology Library v1.02, 'PV (monocrystalline silicon)' sheet, Panel 1</t>
+  </si>
+  <si>
+    <t>Same library as the PV sheet's model default (Panels 16-18 average); Panel 1 is the low-efficiency / low-price end of the range</t>
+  </si>
+  <si>
+    <t>1) Read the Panel 1 row from the CEP library's PV sheet
+2) Set PANEL_1 / PANEL_1_PRICE_PER_WP in pv_panel1_sensitivity.py
+3) Runs automatically at the end of optimisation_model.main(), or standalone: python pv_panel1_sensitivity.py</t>
+  </si>
+  <si>
+    <t>TAXONOMY: model_parameters</t>
+  </si>
+  <si>
     <t xml:space="preserve">- Single source of truth for tunable model parameters across the optimisation model and the demand model. Sheets suffixed '(DM)' hold demand-model parameters; the rest hold optimisation-model parameters. model_params.load_params() maps each sheet back into the module-level dicts/constants. </t>
   </si>
   <si>
+    <t>- The optimisation is a pure linear program: every decision variable is continuous. The binary charge/discharge and import/export mutex formulation was verified lossless against it and removed, so there is no MIP gap or binary setting to record.</t>
+  </si>
+  <si>
+    <t>- Type taxonomy (the Type column; live conditional formatting colours the row — edit via the dropdown):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * Verified assumption — value confirmed against the cited Source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * Verifiable assumption — a specific source exists but the value is not yet confirmed against it; Source lists the citation to check.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * Placeholder — interim value, not yet sourced; Source flags where to look ('TO BE SOURCED — …').</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * Standing assumption — deliberate modelling / design choice or simplification with no single external citation (Source = '-').</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * Status at this revision: all 447 parameter rows across the 13 sheets resolve to Verified (416) or Standing (31) assumptions — no Verifiable or Placeholder rows remain, and no 'TO BE SOURCED' cells are outstanding.</t>
+  </si>
+  <si>
+    <t>- Demand-model coverage &amp; deferrals:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * Included from demand_profile_model.py: heat-pump COP fits + envelopes, boiler efficiency, ground-loop thermal model, EV inputs, and climate/geometry/weekend-scaling constants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * Deferred to inputs.xlsx (data loaded from that workbook, or mappings tightly coupled to it): CIBSE Dashboard, NCM occupancy/setpoints, TM46 adjustment, BEES floor areas + base-load fractions, UKPN EV shape; plus the ACTIVITY_LOOKUP mappings, BASE_LOAD_CFG and area_weights vectors. Handle these when deciding what to do with inputs.xlsx.</t>
+  </si>
+  <si>
+    <t>- Intentionally not in this workbook:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * Derived values: battery chg_eff/disc_eff = sqrt(round_trip_eff); BATT_MAX_KW = c_rate_chg × BATT_MAX_KWH; DAMPING_DEPTH_M = sqrt(2·alpha/omega) and _OMEGA_YR (demand model).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * Solver / structural / calendar constants: timestep (T_RES_H, HH_PER_DAY), HORIZON_YEARS, BATT_MAX_KWH, solver time limit and worker/thread settings (optimisation_config.py); MONTH_DAYS / MONTH_SEASON / MONTHS_ORDER / SEASONS / DAY_TYPES (seasons.py). Model architecture, not empirical inputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * Primary-energy factors are an exception in the other direction: they live on the Scalars sheet (PRIMARY_ENERGY_FACTOR [electricity] = 1.501, [gas] = 1.130 kWh primary / kWh delivered, NCM Modelling Guide Table 32) and are loaded through model_params like any other parameter, but they feed neither OF1 nor OF2 — they are used only for the primary-energy reporting column on the MAC grid.</t>
+  </si>
+  <si>
+    <t>ECONOMICS (cash flows in real terms)</t>
+  </si>
+  <si>
+    <t>- Horizon — see optimisation_config.HORIZON_YEARS.</t>
+  </si>
+  <si>
+    <t>- Real discount rate (WACC / HM Treasury Green Book STPR) — see model_parameters.xlsx: Scalars sheet, discount_rate.</t>
+  </si>
+  <si>
+    <t>- Maintenance and insurance are technology-specific, not one flat percentage: PV maintenance + insurance are £/MW/yr rates (PV sheet); battery and thermal-store maintenance are a % of their own capex/yr (Battery / Thermal Store sheets, maint_pct_capex); heating maintenance is £/kW_th/yr (Heating sheet, maint_per_kwth_per_yr). Only PV carries a separate insurance line.</t>
+  </si>
+  <si>
+    <t>- Real O&amp;M escalation — see Scalars sheet, general_inflation (the model runs in real prices, so this is 0 by construction unless overridden).</t>
+  </si>
+  <si>
+    <t>- All cost vintages are rebased to a common real price-basis year via the UK GDP deflator before use, so PV/battery/heating/carbon figures sourced in different base years are comparable — see Scalars sheet, GDP_DEFLATOR [year] rows, and model_params.py (TARGET_PRICE_YEAR) / each sheet's 'Price Base Year' column.</t>
+  </si>
+  <si>
+    <t>- No separate PV or thermal-store commissioning cost; battery and heat-pump commissioning are folded into their unit capex rates (see BATTERY / HEAT above).</t>
+  </si>
+  <si>
+    <t>- BAU baseline (common to all scenarios) = conventional gas boiler (sized to peak) + grid electricity + gas, no PV/battery/thermal store, with the same new-build/retrofit treatment as the scenario. NPV savings = BAU NPV − scenario NPV; both include heating-plant capex, so heating systems compare fairly.</t>
+  </si>
+  <si>
+    <t>GRID</t>
+  </si>
+  <si>
+    <t>- Per-district connection ceilings — see model_parameters.xlsx: Scalars sheet, GRID_IMPORT_LIMIT_KW [district] / GRID_EXPORT_LIMIT_KW [district] rows (demand-headroom -&gt; import, generation-headroom -&gt; export; see each row's Source column for the originating DNO dataset).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * Import ceiling = the district's published DNO import headroom, applied as-is — there is no floor at the site's own baseline peak. A cell whose demand cannot be served within that headroom is reported Infeasible rather than quietly relaxed, and grid_sensitivity.py then bisects how far the ceiling would have to rise (grid_import_threshold_kw / grid_shortfall_kw).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * Export ceiling = district export limit (PV export is entirely new generation).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- All 9 districts are sourced from their DNO (UKPN, NPg, ENWL+SPM, NGED, SPD, SSEN; see each row's Source cell). </t>
+  </si>
+  <si>
+    <t>- Module geometry and performance (area, rated power, weight, STC efficiency, temperature coefficient, Ross cell-temperature coefficient, inverter efficiency) — see model_parameters.xlsx: PV sheet (each row's Source column).</t>
+  </si>
+  <si>
+    <t>- Cell temperature: T_cell = T_amb + cell_temp_coeff × I (I = irradiance, W/m²) — see PV sheet, cell_temp_coeff.</t>
+  </si>
+  <si>
+    <t>- PV capex = construction cost + infrastructure cost per kWp, each carrying its own DESNZ Low/Central/High scenario (one shared switch for both, Central active by default) — see PV sheet, const_per_kwp / infra_per_kwp, and PV_CAPEX_ACTIVE in model_params.py.</t>
+  </si>
+  <si>
+    <t>- PV and inverter degradation, and inverter replacement year + cost share — see PV sheet, soh_decay_per_yr / soh_inv_decay_per_yr / inv_replace_year / inv_cost_share.</t>
+  </si>
+  <si>
+    <t>- Maintenance and insurance are PV-specific £/MW/yr rates, each with its own Low/Central/High scenario — see PV sheet, maint_per_mw_per_yr / insurance_per_mw_per_yr. PV is the only technology with a separate insurance line (see ECONOMICS).</t>
+  </si>
+  <si>
+    <t>ROOF (per activity class — see ROOF_PROPERTIES)</t>
+  </si>
+  <si>
+    <t>- Roof footprint = BEES floor area / median storeys. Median storeys per activity read from the OpenStreetMap building:levels survey — see api_osm_storeys.py / data/api_osm_storeys.xlsx.</t>
+  </si>
+  <si>
+    <t>- The footprint is split into a flat fraction and a pitched fraction; flat_share is matched to each activity's modelled footprint band — see data/api_osm_storeys.xlsx: 'Flat by Footprint' and model_parameters.xlsx: Roof sheet, ROOF_PITCH_DEG.</t>
+  </si>
+  <si>
+    <t>- Usable PV area = footprint × [ flat_share × pv_usable_frac × pv_inter_row_frac + (1-flat_share) × (1/cos(pitch)) × pitched_usable_slope_frac ],</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  i.e. flat roofs use the literature usable fractions below, further de-rated by inter-row self-shading (flat-roof PV is tilted/rack-mounted); pitched roofs have a larger sloped surface but a smaller usable share after orientation, shading and obstructions, and are mounted flush to the slope so no inter-row spacing applies.</t>
+  </si>
+  <si>
+    <t>- PV-usable fraction and inter-row spacing fraction of FLAT footprint, per activity (plant, rooflights, shading, module spacing, self-shading) — see model_parameters.xlsx: Roof sheet, pv_usable_frac / pv_inter_row_frac (see each row's Source column).</t>
+  </si>
+  <si>
+    <t>- Roof live-load capacity available for PV; see Roof sheet, ROOF_LOAD_KG_PER_M2.</t>
+  </si>
+  <si>
+    <t>BATTERY (Li-ion)</t>
+  </si>
+  <si>
+    <t>- Energy capex, power capex, round-trip efficiency, usable SOC bounds, charge/discharge C-rate limits, degradation rate and replacement year — see model_parameters.xlsx: Battery sheet.</t>
+  </si>
+  <si>
+    <t>- No separate commissioning cost: balance-of-system and commissioning are already embedded in the energy/power capex rates.</t>
+  </si>
+  <si>
+    <t>HEAT: Scenario parameter</t>
+  </si>
+  <si>
+    <t>- Useful thermal demand is tech-independent; same WD/WE scaling as electricity.</t>
+  </si>
+  <si>
+    <t>- Conversion to fuel: gas boiler gas = useful heat / boiler efficiency; heat-pump electricity = useful heat / COP(t) — boiler efficiency and COP curve parameters: see model_parameters.xlsx: 'Heating &amp; COP (DM)' sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  The COP curves themselves live in demand_profile_model.py (cop_ashp / cop_gshp); the half-hourly COP profile per (heating, district, month) is assembled in optimisation_engine.cop_profile() — ASHP follows the outdoor-temperature curve hourly; GSHP follows a flat curve for vertical loops and a month-averaged ground-temperature curve for horizontal loops.</t>
+  </si>
+  <si>
+    <t>- Heating-plant thermal capacity (kW_th) is always sized by the model. Capex and O&amp;M per kW_th for each heating type are on model_parameters.xlsx: Heating sheet (see each row's Type/Source columns); every row is now sourced.</t>
+  </si>
+  <si>
+    <t>- Heat-pump replacement year, and the GSHP HP-unit-vs-ground-loop capex split used at replacement (the loop outlasts the horizon) — see Heating sheet, replace_year / replace_cost_share.</t>
+  </si>
+  <si>
+    <t>- New-build vs retrofit (NEW_BUILD flag, optimisation_config.py): new-build installs a fresh boiler on the BAU and every scenario alike (gas capex cancels for a gas-vs-gas comparison; a heat-pump scenario gets an avoided-boiler credit). Retrofit treats the existing gas boiler as a sunk asset for a gas-boiler scenario (no capex, no replacement) and instead charges a heat-pump scenario a one-off fixed gas-service decommissioning cost with no avoided-boiler credit — see Heating sheet, decommission_fixed.</t>
+  </si>
+  <si>
+    <t>- Thermal store is optional and sized by the model; daily-cycling only (no seasonal storage) — each representative day starts empty. Capex, standing loss, charge/discharge efficiency and replacement year — see model_parameters.xlsx: Thermal Store sheet.</t>
+  </si>
+  <si>
+    <t>- GSHP (horizontal) capacity is capped by on-site land. Soft ground = site area (BEES floor area / SITE_PLOT_RATIO) − roof footprint − parking (EV_PARKING_DENSITY × PARKING_GROSS_M2_PER_SPACE), clamped at 0 m²; the trenched collector then needs HORIZONTAL_COLLECTOR_M2_PER_KWTH per kW_th, giving land_limit_kwth, which bounds q_heat_cap (optimisation_engine.py). Vertical boreholes need negligible surface area and are unconstrained. Parameters and sources: model_parameters.xlsx, Ground Loop (DM) sheet; binding cases are flagged by land_limit_binds in the sweep output.</t>
+  </si>
+  <si>
+    <t>FUEL &amp; ELECTRICITY IMPORT PRICING</t>
+  </si>
+  <si>
+    <t>- Gas import price: DESNZ Quarterly Energy Prices non-domestic size bands (incl. CCL), auto-selected per building by annual gas burned (useful heat / boiler efficiency); real escalation from the active DESNZ gas price-growth scenario — see model_parameters.xlsx: Energy Prices sheet (Gas Import / Energy Price Growth groups).</t>
+  </si>
+  <si>
+    <t>- Electricity import price: a wholesale + regional DUoS build-up (wholesale × half-hourly shape + per-DNO DUoS Red/Amber/Green + CCL + band-specific residual), giving an intra-day, seasonal, regional price rather than one flat rate — see pricing.py and Energy Prices sheet (DUoS Time Band / DUoS Unit Charge / Retail Non-Commodity groups); wholesale level from api_wholesale_prices.py.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Can be switched off in favour of the flat DESNZ band price — see optimisation_config.USE_WHOLESALE_DUOS_BUILDUP.</t>
+  </si>
+  <si>
+    <t>- Export price: SEG Low/Central/High sensitivities; real escalation from the electricity price-growth scenario — see Energy Prices sheet (Electricity Export group).</t>
+  </si>
+  <si>
+    <t>DEMAND</t>
+  </si>
+  <si>
+    <t>- Floor area per activity: BEES median premises floor area (Figure 1.4, England and Wales) — see demand_profile_model.load_bees_floor_areas() for the source workbook/sheet.</t>
+  </si>
+  <si>
+    <t>- Electricity demand: lighting + small power + HVAC + EV + heat-pump electricity (if HP scenario)</t>
+  </si>
+  <si>
+    <t>- Demand grows across the 15-year horizon: non-heat electricity per the DESNZ Reference projection; heat demand falls and heat-pump COP improves as the climate warms, per the UKCP18 projection — see growth.py and datasets.get_electricity_projection() / get_climate_projection() (year-0 = EMISSIONS_BASE_YEAR in model_params.py).</t>
+  </si>
+  <si>
+    <t>- 24 representative days per year: 12 months × {WD, WE}. The WD/WE split applies wd_fac = 7/(5+2f) and we_fac = wd_fac × f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  where f = WE_LOAD_FACTOR[activity] from TM46 operational schedules — see model_params.py.</t>
+  </si>
+  <si>
+    <t>- WD/WE day counts per month are derived from a fixed representative calendar year — see optimisation_config.wd_we_counts_2025().</t>
+  </si>
+  <si>
+    <t>PV irradiance</t>
+  </si>
+  <si>
+    <t>- Per-district daily GHI (kWh/m²/day) from a long-term monthly average, taken directly at each district's reference weather station (see DISTRICT_STATIONS) — no inter-district scaling — see model_parameters.xlsx: GHI sheet (each row's Source column).</t>
+  </si>
+  <si>
+    <t>- Hourly shape from dm.solar_elevation_profile at the parent-season DOY (mid-season solar geometry)</t>
+  </si>
+  <si>
+    <t>- Ambient temperature per month uses monthly HDD via T_amb = T_base − HDD; hourly amplitude from dm.DIURNAL_AMPLITUDE at the parent-season level — see model_params.py, HDD_BASE / DIURNAL_AMPLITUDE.</t>
+  </si>
+  <si>
+    <t>CARBON (OF2) — lifetime operational emissions, kgCO2e</t>
+  </si>
+  <si>
+    <t>- Grid electricity emission factor: long-run marginal, consumption-based (incl. T&amp;D + power-station losses), Commercial/Public sector; a per-year trajectory over the horizon, not a single rate (the grid decarbonises  substantially) — see model_parameters.xlsx: Emissions sheet, Electricity Emission Factor group.</t>
+  </si>
+  <si>
+    <t>- Exported PV is CREDITED at the same long-run-marginal factor (avoided grid generation).</t>
+  </si>
+  <si>
+    <t>- Gas combustion: constant all-GHG factor (gross CV) — see Emissions sheet, Gas Emission Factor group.</t>
+  </si>
+  <si>
+    <t>- Emissions are summed UNDISCOUNTED over the 15-yr horizon. Carbon values are used only for the monetised-carbon and MAC reporting figures, not in OF1 — see Emissions sheet, Carbon Value group.</t>
+  </si>
+  <si>
+    <t>- Three objective views are produced: NPV-min, carbon-min, and the NPV/carbon trade-off. The pooled trade-off set is the non-dominated subset of the two single-objective sweeps, taken within each (district, activity) cell across heating technologies (assemble_pareto — 'Pareto Data' sheet). A true epsilon-constraint frontier — expected carbon capped at a sweep of levels and cost re-minimised at each — is traced separately for the featured cell only (pareto_front in optimisation_engine.py — 'Pareto Front Data' sheet).</t>
+  </si>
+  <si>
+    <t>UNCERTAINTY — TWO-STAGE STOCHASTIC PROGRAM (TSSP)</t>
+  </si>
+  <si>
+    <t>- The model is a two-stage stochastic program. STAGE 1 (here-and-now, shared across all scenarios): the sizing/selection decisions.  STAGE 2 (recourse, per scenario): the half-hourly dispatch, free to re-optimise against each  scenario's realised prices.</t>
+  </si>
+  <si>
+    <t>- The reported design is the single robust stage-1 solution.</t>
+  </si>
+  <si>
+    <t>- Two cost rounds are run and reported side by side: 'deterministic' (the single central price scenario) and 'stochastic' (the reduced weighted scenario set). Each writes its own results workbook and chart set. The deterministic round is also the one every downstream analysis re-solves against.</t>
+  </si>
+  <si>
+    <t>- Uncertain input (this iteration): ELECTRICITY IMPORT price only. Two facets, both sampled:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * level multiplier — triangular(min=Low, mode=Central=1.0, max=High) — see model_parameters.xlsx: Energy Prices sheet, Import Price Scenario group (elec_import_multiplier).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * annual escalation — triangular over the Energy Price Growth electricity band (Low/Central/High) — see Energy Prices sheet, Energy Price Growth group (elec_price_growth).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Level and escalation are sampled independently; each draw -&gt; a 15-yr price path level*(1+growth)^y.</t>
+  </si>
+  <si>
     <t>- Scenario generation: 2-D Latin Hypercube Sampling reduced to a small set of weighted representative  scenarios by k-medoid clustering of the price paths — see uncertainty.py, DEFAULT_N_SAMPLES / DEFAULT_N_REDUCED.</t>
   </si>
   <si>
@@ -811,83 +900,56 @@
     <t>- EMISSIONS objective is price-independent, so it is solved deterministically on a single central scenario (the stochastic structure adds nothing until demand / PV uncertainty is included).</t>
   </si>
   <si>
-    <t xml:space="preserve">    * Verified assumption — value confirmed against the cited Source.</t>
-  </si>
-  <si>
-    <t>- GSHP horizontal-vs-vertical land-area constraint</t>
-  </si>
-  <si>
-    <t>- Intentionally not in this workbook:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- All 9 districts are sourced from their DNO (UKPN, NPg, ENWL+SPM, NGED, SPD, SSEN; see each row's Source cell). </t>
-  </si>
-  <si>
-    <t>- Emissions are summed UNDISCOUNTED over the 15-yr horizon. Carbon values are used only for the monetised-carbon and MAC reporting figures, not in OF1 — see Emissions sheet, Carbon Value group.</t>
-  </si>
-  <si>
-    <t>- Three objective views are produced: NPV-min, carbon-min, and the NPV/carbon Pareto trade-off (assembled across heating technologies from the two single-objective sweeps).</t>
-  </si>
-  <si>
-    <t>- The model is a two-stage stochastic program. STAGE 1 (here-and-now, shared across all scenarios): the sizing/selection decisions.  STAGE 2 (recourse, per scenario): the half-hourly dispatch, free to re-optimise against each  scenario's realised prices.</t>
-  </si>
-  <si>
-    <t>- The reported design is the single robust stage-1 solution.</t>
-  </si>
-  <si>
-    <t>- Real discount rate (WACC / HM Treasury Green Book STPR) — see model_parameters.xlsx: Scalars sheet, discount_rate.</t>
-  </si>
-  <si>
-    <t>- Roof live-load capacity available for PV; see Roof sheet, ROOF_LOAD_KG_PER_M2.</t>
-  </si>
-  <si>
-    <t>- Energy capex, power capex, round-trip efficiency, usable SOC bounds, charge/discharge C-rate limits, degradation rate and replacement year — see model_parameters.xlsx: Battery sheet.</t>
-  </si>
-  <si>
-    <t>- Conversion to fuel: gas boiler gas = useful heat / boiler efficiency; heat-pump electricity = useful heat / COP(t) — boiler efficiency and COP curve parameters: see model_parameters.xlsx: 'Heating &amp; COP (DM)' sheet.</t>
-  </si>
-  <si>
-    <t>- Heating-plant thermal capacity (kW_th) is always sized by the model. Capex and O&amp;M per kW_th for each heating type — and which rows are still placeholders pending sourcing — are on model_parameters.xlsx: Heating sheet (see each row's Type/Source columns).</t>
-  </si>
-  <si>
-    <t>- Per-district connection ceilings — see model_parameters.xlsx: Scalars sheet, GRID_IMPORT_LIMIT_KW [district] / GRID_EXPORT_LIMIT_KW [district] rows (demand-headroom -&gt; import, generation-headroom -&gt; export; see each row's Source column for the originating DNO dataset).</t>
-  </si>
-  <si>
-    <t>- Module geometry and performance (area, rated power, weight, STC efficiency, temperature coefficient, Ross cell-temperature coefficient, inverter efficiency) — see model_parameters.xlsx: PV sheet (each row's Source column).</t>
-  </si>
-  <si>
-    <t>- The footprint is split into a flat fraction and a pitched fraction; flat_share is matched to each activity's modelled footprint band — see data/api_osm_storeys.xlsx: 'Flat by Footprint' and model_parameters.xlsx: Roof sheet, ROOF_PITCH_DEG.</t>
-  </si>
-  <si>
-    <t>- PV-usable fraction and inter-row spacing fraction of FLAT footprint, per activity (plant, rooflights, shading, module spacing, self-shading) — see model_parameters.xlsx: Roof sheet, pv_usable_frac / pv_inter_row_frac (see each row's Source column).</t>
-  </si>
-  <si>
-    <t>- Thermal store is optional and sized by the model; daily-cycling only (no seasonal storage) — each representative day starts empty. Capex, standing loss, charge/discharge efficiency and replacement year — see model_parameters.xlsx: Thermal Store sheet.</t>
-  </si>
-  <si>
-    <t>- Gas import price: DESNZ Quarterly Energy Prices non-domestic size bands (incl. CCL), auto-selected per building by annual gas burned (useful heat / boiler efficiency); real escalation from the active DESNZ gas price-growth scenario — see model_parameters.xlsx: Energy Prices sheet (Gas Import / Energy Price Growth groups).</t>
-  </si>
-  <si>
-    <t>- Per-district daily GHI (kWh/m²/day) from a long-term monthly average, taken directly at each district's reference weather station (see DISTRICT_STATIONS) — no inter-district scaling — see model_parameters.xlsx: GHI sheet (each row's Source column).</t>
-  </si>
-  <si>
-    <t>- Grid electricity emission factor: long-run marginal, consumption-based (incl. T&amp;D + power-station losses), Commercial/Public sector; a per-year trajectory over the horizon, not a single rate (the grid decarbonises  substantially) — see model_parameters.xlsx: Emissions sheet, Electricity Emission Factor group.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    * level multiplier — triangular(min=Low, mode=Central=1.0, max=High) — see model_parameters.xlsx: Energy Prices sheet, Import Price Scenario group (elec_import_multiplier).</t>
-  </si>
-  <si>
-    <t>TAXONOMY: model_parameters</t>
-  </si>
-  <si>
-    <t>ECONOMICS (cash flows in real terms)</t>
+    <t>DOWNSTREAM ANALYSIS (all run off the deterministic cost round)</t>
+  </si>
+  <si>
+    <t>- Grid headroom margin (grid_sensitivity.py), per (district, activity) × heat-pump cell. Feasible cells: bisects a uniform demand-level multiplier upward until the cell turns infeasible, reported as demand_growth_margin_pct — how much further demand growth the present-day grid ceiling can absorb. Infeasible cells: bisects the import-ceiling override upward until the cell solves, reported as grid_import_threshold_kw / grid_shortfall_kw. Each trial pins stage-1 sizing to the baseline design (fixed n_pv, fixed thermal store, no battery) and runs on the deterministic price scenario, since feasibility is a physical property of demand / COP / headroom shared across price scenarios. Gas Boiler is out of scope (it draws no heat-pump electricity).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    * The margin is per building and is an UPPER BOUND: the DNO headroom is already net of everything currently connected, but the whole of that spare capacity is allocated to this one site, with no other connection behind the same substation assumed to grow.</t>
+  </si>
+  <si>
+    <t>- Policy levers (policy_recommendations.py), back-calculated once per activity class at that class's own best-NPV district, so a recommendation can be targeted by end-user type and location: (1) the battery capex rebate that makes storage NPV-recommended; (2) the heat-pump capex rebate that undercuts the gas boiler; (3) the uniform electricity import-price cut that does the same, anchored at 0% and 100% HP capex rebate, with the gas boiler re-solved under the same cut for a fair comparison; (4) the SEG export-price multiple that makes storage pay on export alone; and (5) a step-wise 0-to-100% battery capex grant sweep in 5% steps, showing what each increment buys, its cost per kWh installed, and how much comes back as NPV gain to the end user.</t>
+  </si>
+  <si>
+    <t>- Technology sensitivities. Both fix stage-1 sizing at the saved deterministic design and re-solve stage-2 dispatch only, so they isolate the technology change rather than re-optimising around it. ASHP: Grant Aerona3 R32, COP @ A7/W55 = 2.66 against the model's 2.7283, paired with a 2.6% capex cut (ashp_grant_aerona3_sensitivity.py). PV: CEP library Panel 1 substituted for the Panels 16-18 default, area-matched so n_pv is rescaled to hold roof area constant and capex scaled by the price ratio (pv_panel1_sensitivity.py).</t>
+  </si>
+  <si>
+    <t>- DEC validation (scripts/dec_validation.py). Modelled year-0 energy intensities against metered Display Energy Certificates. This exists to break the circularity in the electricity arm of the benchmark comparison, where the modelled non-EV electricity IS the CIBSE benchmark, so comparing it against a benchmark survey only tests one benchmark against another; the DEC 'annual_*' fields are metered actuals and sit outside the whole build-up. Modelled useful heat is divided by boiler efficiency to match DEC's delivered-fuel convention, and modelled electricity is reported both including and excluding the assumed EV charging layer. Sample caveat: public-authority stock at or above 250 m² only.</t>
+  </si>
+  <si>
+    <t>OUT OF SCOPE</t>
+  </si>
+  <si>
+    <t>- Seasonal (inter-day) thermal storage; the buffer store is daily-cycling only</t>
+  </si>
+  <si>
+    <t>- Demand response / load shifting</t>
+  </si>
+  <si>
+    <t>- Embodied / lifecycle carbon of PV, battery, heat-pump plant (no UK-gov source; operational only)</t>
+  </si>
+  <si>
+    <t>- Uncertainty in demand, PV generation, gas and carbon prices (only electricity import price is built in)</t>
+  </si>
+  <si>
+    <t>- Frequency response revenue</t>
+  </si>
+  <si>
+    <t>1) Download the DEC bulk 'display-csv' extract from the register</t>
+  </si>
+  <si>
+    <t>- Panel 1: 17.52% efficiency, -0.40%/K temperature coefficient, 0.285 kWp, 1.63 m2, GBP 0.4737/Wp
+- Panels 16-18 default of 20.9%, -0.26%/K, 0.365 kWp, 1.75 m2, GBP 0.6636/Wp. 
+- Area-matched substitution: n_pv is rescaled so the Panel 1 array occupies the same roof area, with capex scaled by the price ratio. 
+- Stage-1 sizing is fixed at the saved deterministic design; only stage-2 dispatch is re-solved</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -939,10 +1001,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -987,7 +1052,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1017,7 +1082,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1314,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.6328125" style="7" bestFit="1" customWidth="1"/>
@@ -1325,754 +1391,808 @@
     <col min="6" max="6" width="54.54296875" style="8" customWidth="1"/>
     <col min="7" max="7" width="43.08984375" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="42.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="8.7265625" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.7265625" style="6"/>
+    <col min="9" max="11" width="8.7265625" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>69</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>111</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>122</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H9" s="9"/>
     </row>
     <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>137</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>138</v>
+        <v>74</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>143</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>151</v>
+        <v>87</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>152</v>
+        <v>88</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>153</v>
+        <v>89</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>154</v>
+        <v>90</v>
       </c>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>155</v>
+        <v>91</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>157</v>
+        <v>93</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>158</v>
+        <v>94</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>163</v>
+        <v>99</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>167</v>
+        <v>103</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>168</v>
+        <v>104</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>169</v>
+        <v>105</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>171</v>
+        <v>107</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>172</v>
+        <v>61</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>173</v>
+        <v>109</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G17" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H17" s="9" t="s">
-        <v>176</v>
+      <c r="F17" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>178</v>
+        <v>114</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>179</v>
+        <v>115</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>181</v>
+        <v>117</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>182</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>184</v>
+        <v>119</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>186</v>
+        <v>121</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>187</v>
+        <v>122</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>188</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>189</v>
+        <v>123</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>190</v>
+        <v>125</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>191</v>
+        <v>126</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>192</v>
+        <v>127</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>193</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H20" s="9"/>
     </row>
     <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>194</v>
+        <v>128</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>196</v>
+        <v>130</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>197</v>
+        <v>131</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>199</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H21" s="9"/>
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>202</v>
+        <v>135</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>203</v>
+        <v>136</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>204</v>
+        <v>137</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>205</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H22" s="9"/>
     </row>
     <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>206</v>
+        <v>138</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>207</v>
+        <v>139</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>208</v>
+        <v>140</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>209</v>
+        <v>141</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>210</v>
+        <v>142</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>211</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H23" s="9"/>
     </row>
     <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>212</v>
+        <v>143</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>213</v>
+        <v>144</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>214</v>
+        <v>145</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>215</v>
+        <v>146</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>216</v>
+        <v>147</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>217</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H24" s="9"/>
     </row>
     <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>218</v>
+        <v>148</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>219</v>
+        <v>149</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>221</v>
+        <v>151</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>222</v>
+        <v>152</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>223</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H25" s="9"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>224</v>
+        <v>153</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>225</v>
+        <v>154</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>226</v>
+        <v>155</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>227</v>
+        <v>156</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>228</v>
+        <v>157</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>229</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>230</v>
+        <v>159</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>231</v>
+        <v>43</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>232</v>
+        <v>161</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>234</v>
+        <v>163</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>236</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H27" s="9"/>
     </row>
     <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>238</v>
+        <v>165</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>239</v>
+        <v>166</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>240</v>
+        <v>167</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>241</v>
+        <v>168</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>243</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>244</v>
+        <v>171</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>246</v>
+        <v>61</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>247</v>
+        <v>173</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>248</v>
+        <v>174</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>249</v>
+        <v>175</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>250</v>
+        <v>176</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>251</v>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2090,25 +2210,13 @@
     <hyperlink ref="H4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="H5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="H6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="H7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="H9" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="H11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="H12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="H15" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="H16" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="H17" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="H18" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="H19" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="H20" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="H21" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="H22" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="H23" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="H24" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="H25" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="H26" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="H27" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="H28" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="H29" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="H11" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="H12" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="H15" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="H16" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="H17" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="H28" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="H29" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2116,462 +2224,549 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A103"/>
+  <dimension ref="A1:A114"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
-        <v>279</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>252</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>53</v>
+      <c r="A3" s="12" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>257</v>
+      <c r="A4" s="12" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>54</v>
+      <c r="A5" s="12" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>55</v>
+      <c r="A6" s="12" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>56</v>
+      <c r="A7" s="12" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>57</v>
+      <c r="A8" s="12" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>58</v>
+      <c r="A9" s="12" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>59</v>
+      <c r="A10" s="12" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>259</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>60</v>
+      <c r="A12" s="12" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>61</v>
+      <c r="A13" s="12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" s="12" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
-        <v>280</v>
+      <c r="A15" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>31</v>
+      <c r="A16" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
-        <v>265</v>
-      </c>
+      <c r="A17" s="11"/>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>32</v>
+      <c r="A18" s="10" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>33</v>
+      <c r="A19" s="12" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>34</v>
+      <c r="A20" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>35</v>
+      <c r="A21" s="12" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>36</v>
+      <c r="A22" s="12" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="12" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" s="10" t="s">
-        <v>37</v>
+      <c r="A24" s="12" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>270</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>38</v>
-      </c>
+      <c r="A26" s="12"/>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>39</v>
+      <c r="A27" s="10" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>260</v>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" s="12" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" s="10" t="s">
-        <v>7</v>
+      <c r="A30" s="12" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>271</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>8</v>
-      </c>
+      <c r="A32" s="12"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>9</v>
+      <c r="A33" s="10" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>10</v>
+      <c r="A34" s="12" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>11</v>
+      <c r="A35" s="12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="12" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" s="10" t="s">
-        <v>24</v>
+      <c r="A37" s="12" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>25</v>
+      <c r="A38" s="12" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" s="11" t="s">
-        <v>272</v>
-      </c>
+      <c r="A39" s="11"/>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>26</v>
+      <c r="A40" s="10" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>27</v>
+      <c r="A41" s="12" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="11" t="s">
-        <v>273</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
-        <v>266</v>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="12" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" s="10" t="s">
-        <v>12</v>
+      <c r="A45" s="12" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" s="11" t="s">
-        <v>267</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>13</v>
+      <c r="A47" s="12"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" s="10" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" s="10" t="s">
-        <v>14</v>
+      <c r="A49" s="12" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>15</v>
+      <c r="A50" s="12" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A51" s="11" t="s">
-        <v>268</v>
-      </c>
+      <c r="A51" s="11"/>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>16</v>
+      <c r="A52" s="10" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="11" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>17</v>
+      <c r="A54" s="12" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>18</v>
+      <c r="A55" s="12" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" s="11" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>19</v>
+      <c r="A57" s="12" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" s="12" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A59" s="10" t="s">
-        <v>20</v>
+      <c r="A59" s="12" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" s="11" t="s">
-        <v>275</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>21</v>
-      </c>
+      <c r="A61" s="12"/>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>22</v>
+      <c r="A62" s="10" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>23</v>
+      <c r="A63" s="12" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" s="12" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" s="10" t="s">
-        <v>0</v>
+      <c r="A65" s="12" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>1</v>
+      <c r="A66" s="12" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>2</v>
-      </c>
+      <c r="A67" s="12"/>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>3</v>
+      <c r="A68" s="10" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>4</v>
+      <c r="A69" s="12" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>5</v>
+      <c r="A70" s="12" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>6</v>
+      <c r="A71" s="12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" s="12" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A73" s="10" t="s">
-        <v>28</v>
+      <c r="A73" s="12" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" s="11" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>29</v>
-      </c>
+      <c r="A75" s="12"/>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>30</v>
+      <c r="A76" s="10" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" s="12" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A78" s="10" t="s">
-        <v>44</v>
+      <c r="A78" s="12" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" s="11" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>45</v>
-      </c>
+      <c r="A80" s="12"/>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>46</v>
+      <c r="A81" s="10" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" s="11" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" s="11" t="s">
-        <v>262</v>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" s="12" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A85" s="10" t="s">
-        <v>40</v>
+      <c r="A85" s="12" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" s="11" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A87" s="11" t="s">
-        <v>264</v>
-      </c>
+      <c r="A87" s="11"/>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>41</v>
+      <c r="A88" s="10" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>278</v>
+      <c r="A89" s="12" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>42</v>
+      <c r="A90" s="12" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>43</v>
+      <c r="A91" s="12" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" s="11" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>254</v>
+      <c r="A93" s="12" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" s="11" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" s="11" t="s">
-        <v>256</v>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A96" s="12" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A97" s="10" t="s">
-        <v>47</v>
+      <c r="A97" s="12" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" s="11" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>48</v>
+      <c r="A99" s="12" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>49</v>
-      </c>
+      <c r="A100" s="12"/>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>50</v>
-      </c>
+      <c r="A101" s="12"/>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>51</v>
+      <c r="A102" s="10" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>52</v>
+      <c r="A103" s="12" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" s="12" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A105" s="12" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A106" s="12" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A107" s="12" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A108" s="12"/>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A109" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A110" s="12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A111" s="12" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A112" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A113" s="12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A114" s="12" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>
